--- a/e2e-screenshots/orphan-completion/fixtures/SALES_ORPHAN_TEST.xlsx
+++ b/e2e-screenshots/orphan-completion/fixtures/SALES_ORPHAN_TEST.xlsx
@@ -451,7 +451,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-07-30</v>
+        <v>2026-08-02</v>
       </c>
       <c r="B2" t="str">
         <v>ORPHAN-TEST-1</v>

--- a/e2e-screenshots/orphan-completion/fixtures/SALES_ORPHAN_TEST.xlsx
+++ b/e2e-screenshots/orphan-completion/fixtures/SALES_ORPHAN_TEST.xlsx
@@ -451,7 +451,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-02</v>
+        <v>2026-08-03</v>
       </c>
       <c r="B2" t="str">
         <v>ORPHAN-TEST-1</v>

--- a/e2e-screenshots/orphan-completion/fixtures/SALES_ORPHAN_TEST.xlsx
+++ b/e2e-screenshots/orphan-completion/fixtures/SALES_ORPHAN_TEST.xlsx
@@ -451,7 +451,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-03</v>
+        <v>2026-08-07</v>
       </c>
       <c r="B2" t="str">
         <v>ORPHAN-TEST-1</v>

--- a/e2e-screenshots/orphan-completion/fixtures/SALES_ORPHAN_TEST.xlsx
+++ b/e2e-screenshots/orphan-completion/fixtures/SALES_ORPHAN_TEST.xlsx
@@ -451,7 +451,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-08-07</v>
+        <v>2026-08-08</v>
       </c>
       <c r="B2" t="str">
         <v>ORPHAN-TEST-1</v>
